--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -1821,11 +1821,11 @@
         <v>118319293</v>
       </c>
       <c r="B12" t="n">
-        <v>57306</v>
+        <v>57381</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Limberget, kalkbrottet  (Limberget), Vstm</t>
+          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>118319293</v>
       </c>
       <c r="B12" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>118319293</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Camilla Pettersson, Anders Carlberg, Kjell Sundkvist</t>
+          <t>Kjell Sundkvist, Anders Carlberg, Camilla Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -1836,11 +1836,6 @@
       <c r="E12" t="n">
         <v>100049</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -1821,7 +1821,7 @@
         <v>118319293</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,6 +1835,11 @@
       </c>
       <c r="E12" t="n">
         <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kjell Sundkvist, Anders Carlberg, Camilla Pettersson</t>
+          <t>Camilla Pettersson, Anders Carlberg, Kjell Sundkvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,70 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110278643</v>
+        <v>118319293</v>
       </c>
       <c r="B2" t="n">
-        <v>5207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100155</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre timmerman</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acanthocinus griseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käppstaberget, vägen upp., Vstm</t>
+          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497738.2683432935</v>
+        <v>497758</v>
       </c>
       <c r="R2" t="n">
-        <v>6595216.332337606</v>
+        <v>6595460</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,27 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På talltimmerupplag.</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,19 +778,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Camilla Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Camilla Pettersson, Anders Carlberg, Kjell Sundkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -813,12 +799,7 @@
         <v>118318369</v>
       </c>
       <c r="B3" t="n">
-        <v>97828</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,14 +827,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limberget, kalkbrottet  (Limberget), Vstm</t>
+          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>497758</v>
       </c>
       <c r="R3" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -922,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118318304</v>
+        <v>118318376</v>
       </c>
       <c r="B4" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,34 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Limberget, kalkbrottet  (Limberget), Vstm</t>
+          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>497758</v>
       </c>
       <c r="R4" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1034,15 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118318248</v>
+        <v>118318304</v>
       </c>
       <c r="B5" t="n">
-        <v>103356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käppstaviken (Käppstaviken), Vstm</t>
+          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>497758</v>
       </c>
       <c r="R5" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1109,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,32 +1117,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118318428</v>
+        <v>118319575</v>
       </c>
       <c r="B6" t="n">
-        <v>100024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1182,14 +1148,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Limberget, kalkbrottet  (Limberget), Vstm</t>
+          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>497758</v>
       </c>
       <c r="R6" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1221,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118319171</v>
+        <v>118317986</v>
       </c>
       <c r="B7" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,34 +1235,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Limberget (Limberget), Vstm</t>
+          <t>Käppstaviken, Käppstaviken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>497758</v>
       </c>
       <c r="R7" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1333,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,32 +1331,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118319575</v>
+        <v>118318712</v>
       </c>
       <c r="B8" t="n">
-        <v>105502</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>222361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,14 +1362,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Limberget, kalkbrottet  (Limberget), Vstm</t>
+          <t>Limberget, Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>497758</v>
       </c>
       <c r="R8" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1445,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,15 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118317986</v>
+        <v>118318248</v>
       </c>
       <c r="B9" t="n">
-        <v>96811</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,16 +1449,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,14 +1469,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Käppstaviken (Käppstaviken), Vstm</t>
+          <t>Käppstaviken, Käppstaviken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>497758</v>
       </c>
       <c r="R9" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1557,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,15 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118318376</v>
+        <v>118319171</v>
       </c>
       <c r="B10" t="n">
-        <v>97831</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,34 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Limberget, kalkbrottet  (Limberget), Vstm</t>
+          <t>Limberget, Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>497758</v>
       </c>
       <c r="R10" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1669,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,32 +1652,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118318712</v>
+        <v>118318428</v>
       </c>
       <c r="B11" t="n">
-        <v>98600</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222361</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1742,14 +1683,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Limberget (Limberget), Vstm</t>
+          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>497758</v>
       </c>
       <c r="R11" t="n">
-        <v>6595459</v>
+        <v>6595460</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1781,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,132 +1756,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>118319293</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Limberget, kalkbrottet , Limberget, Vstm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>497758</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6595459</v>
-      </c>
-      <c r="S12" t="n">
-        <v>20</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Camilla Pettersson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Camilla Pettersson, Anders Carlberg, Kjell Sundkvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44844-2022 artfynd.xlsx
+++ b/artfynd/A 44844-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118319293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118318369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118318376</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118318304</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118319575</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118317986</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118318712</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118318248</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118319171</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,8 +1806,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118318428</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>